--- a/test-cases/authentication/android-authentication-session-test-cases.xlsx
+++ b/test-cases/authentication/android-authentication-session-test-cases.xlsx
@@ -11,7 +11,7 @@
     <sheet name="android-auth-session-cases" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'android-auth-session-cases'!$A$1:$L$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'android-auth-session-cases'!$A$1:$I$10</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -23,23 +23,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="65">
   <si>
     <t xml:space="preserve">Test Case ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Feature Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Function</t>
-  </si>
-  <si>
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Preconditions</t>
-  </si>
-  <si>
     <t xml:space="preserve">Test Data ID</t>
   </si>
   <si>
@@ -64,16 +55,7 @@
     <t xml:space="preserve">TC-070</t>
   </si>
   <si>
-    <t xml:space="preserve">Android Authentication and Sessions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Register</t>
-  </si>
-  <si>
     <t xml:space="preserve">Register a new account using valid information.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Android app is installed; the backend is reachable; the username and email do not already exist.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_AUTH_REGISTER_VALID_001</t>
@@ -97,13 +79,7 @@
     <t xml:space="preserve">TC-071</t>
   </si>
   <si>
-    <t xml:space="preserve">Register validation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Submit the registration form with all required fields empty.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Register screen is open.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_AUTH_REGISTER_EMPTY_001</t>
@@ -162,13 +138,7 @@
     <t xml:space="preserve">TC-074</t>
   </si>
   <si>
-    <t xml:space="preserve">Login</t>
-  </si>
-  <si>
     <t xml:space="preserve">Log in using a valid username and password.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The prepared account is ACTIVE; the app has no current session; the backend is reachable.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_AUTH_ACCOUNT_VALID_001</t>
@@ -191,9 +161,6 @@
     <t xml:space="preserve">Reject login when the password is incorrect.</t>
   </si>
   <si>
-    <t xml:space="preserve">The prepared account exists and is ACTIVE; the Login screen is open.</t>
-  </si>
-  <si>
     <t xml:space="preserve">TD_ANDROID_AUTH_LOGIN_WRONG_PASSWORD_001</t>
   </si>
   <si>
@@ -211,13 +178,7 @@
     <t xml:space="preserve">TC-076</t>
   </si>
   <si>
-    <t xml:space="preserve">Login validation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Reject an email address entered in the username field.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Login screen is open.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_AUTH_LOGIN_EMAIL_001</t>
@@ -237,13 +198,7 @@
     <t xml:space="preserve">TC-077</t>
   </si>
   <si>
-    <t xml:space="preserve">Session restoration</t>
-  </si>
-  <si>
     <t xml:space="preserve">Restore a valid session after the Android app is force-stopped and reopened.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A successful session has been created with the prepared account; the backend remains reachable.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_AUTH_ACCOUNT_VALID_001; TD_ANDROID_SESSION_RELAUNCH_001</t>
@@ -267,13 +222,7 @@
     <t xml:space="preserve">TC-078</t>
   </si>
   <si>
-    <t xml:space="preserve">Logout</t>
-  </si>
-  <si>
     <t xml:space="preserve">Log out and verify that the local session is cleared.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The user is logged in with the prepared account.</t>
   </si>
   <si>
     <t xml:space="preserve">TD_ANDROID_AUTH_ACCOUNT_VALID_001; TD_ANDROID_SESSION_LOGOUT_001</t>
@@ -298,7 +247,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -320,6 +269,13 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -364,16 +320,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -587,21 +547,18 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L1048576"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="10.4921875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="64.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="84.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="72.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="137.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="106.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="44.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="49.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="62.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="84.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="37.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="99.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="43.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="33.07"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="2" width="10.49"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -632,337 +589,246 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="D2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="F2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="0" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="F3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="4" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="D4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="0" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I3" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="D5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="0" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="J4" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="0" t="s">
+      <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E5" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="0" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="0" t="s">
+      <c r="D7" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="E7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="F7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="F6" s="0" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="J6" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="0" t="s">
+      <c r="D8" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="E8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="0" t="s">
+      <c r="F8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="0" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="0" t="s">
+      <c r="D9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="I7" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="J7" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="0" t="s">
+      <c r="E9" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="F9" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="0" t="s">
+      <c r="I9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="0" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H8" s="0" t="s">
+      <c r="E10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="0" t="s">
+      <c r="F10" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="J8" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="0" t="s">
+      <c r="G10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B9" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>67</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>68</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="I9" s="0" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="L9" s="0" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>75</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>77</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H10" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="I10" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="J10" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="0" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <autoFilter ref="A1:L10"/>
+  <autoFilter ref="A1:I10"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
